--- a/automated_test/load_report.xlsx
+++ b/automated_test/load_report.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:22</t>
+          <t>2026-07-27 03:26:11</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:22.930</t>
+          <t>2026-07-27 03:25:11.604</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:23.100</t>
+          <t>2026-07-27 03:25:11.774</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:23.270</t>
+          <t>2026-07-27 03:25:11.944</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:23.440</t>
+          <t>2026-07-27 03:25:12.114</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:23.610</t>
+          <t>2026-07-27 03:25:12.284</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:23.780</t>
+          <t>2026-07-27 03:25:12.454</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:23.950</t>
+          <t>2026-07-27 03:25:12.624</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:24.120</t>
+          <t>2026-07-27 03:25:12.794</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:24.290</t>
+          <t>2026-07-27 03:25:12.964</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:24.460</t>
+          <t>2026-07-27 03:25:13.134</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:24.630</t>
+          <t>2026-07-27 03:25:13.304</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:24.800</t>
+          <t>2026-07-27 03:25:13.474</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:24.970</t>
+          <t>2026-07-27 03:25:13.644</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:25.140</t>
+          <t>2026-07-27 03:25:13.814</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:25.310</t>
+          <t>2026-07-27 03:25:13.984</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:25.480</t>
+          <t>2026-07-27 03:25:14.154</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:25.650</t>
+          <t>2026-07-27 03:25:14.324</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:25.820</t>
+          <t>2026-07-27 03:25:14.494</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:25.990</t>
+          <t>2026-07-27 03:25:14.664</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:26.160</t>
+          <t>2026-07-27 03:25:14.834</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:26.330</t>
+          <t>2026-07-27 03:25:15.004</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:26.500</t>
+          <t>2026-07-27 03:25:15.174</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:26.670</t>
+          <t>2026-07-27 03:25:15.344</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:26.840</t>
+          <t>2026-07-27 03:25:15.514</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:27.010</t>
+          <t>2026-07-27 03:25:15.684</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:27.180</t>
+          <t>2026-07-27 03:25:15.854</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:27.350</t>
+          <t>2026-07-27 03:25:16.024</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:27.520</t>
+          <t>2026-07-27 03:25:16.194</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:27.690</t>
+          <t>2026-07-27 03:25:16.364</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:27.860</t>
+          <t>2026-07-27 03:25:16.534</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:28.030</t>
+          <t>2026-07-27 03:25:16.704</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:28.200</t>
+          <t>2026-07-27 03:25:16.874</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:28.370</t>
+          <t>2026-07-27 03:25:17.044</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:28.540</t>
+          <t>2026-07-27 03:25:17.214</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:28.710</t>
+          <t>2026-07-27 03:25:17.384</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:28.880</t>
+          <t>2026-07-27 03:25:17.554</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:29.050</t>
+          <t>2026-07-27 03:25:17.724</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:29.220</t>
+          <t>2026-07-27 03:25:17.894</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:29.390</t>
+          <t>2026-07-27 03:25:18.064</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:29.560</t>
+          <t>2026-07-27 03:25:18.234</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:29.730</t>
+          <t>2026-07-27 03:25:18.404</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:29.900</t>
+          <t>2026-07-27 03:25:18.574</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:30.070</t>
+          <t>2026-07-27 03:25:18.744</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:30.240</t>
+          <t>2026-07-27 03:25:18.914</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:30.410</t>
+          <t>2026-07-27 03:25:19.084</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:30.580</t>
+          <t>2026-07-27 03:25:19.254</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:30.750</t>
+          <t>2026-07-27 03:25:19.424</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:30.920</t>
+          <t>2026-07-27 03:25:19.594</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:31.090</t>
+          <t>2026-07-27 03:25:19.764</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:31.260</t>
+          <t>2026-07-27 03:25:19.934</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:31.430</t>
+          <t>2026-07-27 03:25:20.104</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:31.600</t>
+          <t>2026-07-27 03:25:20.274</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:31.770</t>
+          <t>2026-07-27 03:25:20.444</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:31.940</t>
+          <t>2026-07-27 03:25:20.614</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:32.110</t>
+          <t>2026-07-27 03:25:20.784</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:32.280</t>
+          <t>2026-07-27 03:25:20.954</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:32.450</t>
+          <t>2026-07-27 03:25:21.124</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:32.620</t>
+          <t>2026-07-27 03:25:21.294</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:32.790</t>
+          <t>2026-07-27 03:25:21.464</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:32.960</t>
+          <t>2026-07-27 03:25:21.634</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:33.130</t>
+          <t>2026-07-27 03:25:21.804</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:33.300</t>
+          <t>2026-07-27 03:25:21.974</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:33.470</t>
+          <t>2026-07-27 03:25:22.144</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:33.640</t>
+          <t>2026-07-27 03:25:22.314</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:33.810</t>
+          <t>2026-07-27 03:25:22.484</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:33.980</t>
+          <t>2026-07-27 03:25:22.654</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:34.150</t>
+          <t>2026-07-27 03:25:22.824</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:34.320</t>
+          <t>2026-07-27 03:25:22.994</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:34.490</t>
+          <t>2026-07-27 03:25:23.164</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:34.660</t>
+          <t>2026-07-27 03:25:23.334</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:34.830</t>
+          <t>2026-07-27 03:25:23.504</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:35.000</t>
+          <t>2026-07-27 03:25:23.674</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:35.170</t>
+          <t>2026-07-27 03:25:23.844</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:35.340</t>
+          <t>2026-07-27 03:25:24.014</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:35.510</t>
+          <t>2026-07-27 03:25:24.184</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:35.680</t>
+          <t>2026-07-27 03:25:24.354</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:35.850</t>
+          <t>2026-07-27 03:25:24.524</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:36.020</t>
+          <t>2026-07-27 03:25:24.694</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:36.190</t>
+          <t>2026-07-27 03:25:24.864</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:36.360</t>
+          <t>2026-07-27 03:25:25.034</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:36.530</t>
+          <t>2026-07-27 03:25:25.204</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:36.700</t>
+          <t>2026-07-27 03:25:25.374</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:36.870</t>
+          <t>2026-07-27 03:25:25.544</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:37.040</t>
+          <t>2026-07-27 03:25:25.714</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:37.210</t>
+          <t>2026-07-27 03:25:25.884</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:37.380</t>
+          <t>2026-07-27 03:25:26.054</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:37.550</t>
+          <t>2026-07-27 03:25:26.224</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:37.720</t>
+          <t>2026-07-27 03:25:26.394</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:37.890</t>
+          <t>2026-07-27 03:25:26.564</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:38.060</t>
+          <t>2026-07-27 03:25:26.734</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:38.230</t>
+          <t>2026-07-27 03:25:26.904</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:38.400</t>
+          <t>2026-07-27 03:25:27.074</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:38.570</t>
+          <t>2026-07-27 03:25:27.244</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:38.740</t>
+          <t>2026-07-27 03:25:27.414</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:38.910</t>
+          <t>2026-07-27 03:25:27.584</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:39.080</t>
+          <t>2026-07-27 03:25:27.754</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:39.250</t>
+          <t>2026-07-27 03:25:27.924</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:39.420</t>
+          <t>2026-07-27 03:25:28.094</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:39.590</t>
+          <t>2026-07-27 03:25:28.264</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:39.760</t>
+          <t>2026-07-27 03:25:28.434</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:39.930</t>
+          <t>2026-07-27 03:25:28.604</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:40.100</t>
+          <t>2026-07-27 03:25:28.774</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:40.270</t>
+          <t>2026-07-27 03:25:28.944</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:40.440</t>
+          <t>2026-07-27 03:25:29.114</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:40.610</t>
+          <t>2026-07-27 03:25:29.284</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:40.780</t>
+          <t>2026-07-27 03:25:29.454</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:40.950</t>
+          <t>2026-07-27 03:25:29.624</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:41.120</t>
+          <t>2026-07-27 03:25:29.794</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:41.290</t>
+          <t>2026-07-27 03:25:29.964</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:41.460</t>
+          <t>2026-07-27 03:25:30.134</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:41.630</t>
+          <t>2026-07-27 03:25:30.304</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:41.800</t>
+          <t>2026-07-27 03:25:30.474</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:41.970</t>
+          <t>2026-07-27 03:25:30.644</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:42.140</t>
+          <t>2026-07-27 03:25:30.814</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:42.310</t>
+          <t>2026-07-27 03:25:30.984</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:42.480</t>
+          <t>2026-07-27 03:25:31.154</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:42.650</t>
+          <t>2026-07-27 03:25:31.324</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:42.820</t>
+          <t>2026-07-27 03:25:31.494</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:42.990</t>
+          <t>2026-07-27 03:25:31.664</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:43.160</t>
+          <t>2026-07-27 03:25:31.834</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:43.330</t>
+          <t>2026-07-27 03:25:32.004</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:43.500</t>
+          <t>2026-07-27 03:25:32.174</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:43.670</t>
+          <t>2026-07-27 03:25:32.344</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:43.840</t>
+          <t>2026-07-27 03:25:32.514</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:44.010</t>
+          <t>2026-07-27 03:25:32.684</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:44.180</t>
+          <t>2026-07-27 03:25:32.854</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:44.350</t>
+          <t>2026-07-27 03:25:33.024</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:44.520</t>
+          <t>2026-07-27 03:25:33.194</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:44.690</t>
+          <t>2026-07-27 03:25:33.364</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:44.860</t>
+          <t>2026-07-27 03:25:33.534</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:45.030</t>
+          <t>2026-07-27 03:25:33.704</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:45.200</t>
+          <t>2026-07-27 03:25:33.874</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:45.370</t>
+          <t>2026-07-27 03:25:34.044</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:45.540</t>
+          <t>2026-07-27 03:25:34.214</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:45.710</t>
+          <t>2026-07-27 03:25:34.384</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="I137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:45.880</t>
+          <t>2026-07-27 03:25:34.554</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:46.050</t>
+          <t>2026-07-27 03:25:34.724</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:46.220</t>
+          <t>2026-07-27 03:25:34.894</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:46.390</t>
+          <t>2026-07-27 03:25:35.064</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="I141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:46.560</t>
+          <t>2026-07-27 03:25:35.234</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:46.730</t>
+          <t>2026-07-27 03:25:35.404</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:46.900</t>
+          <t>2026-07-27 03:25:35.574</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:47.070</t>
+          <t>2026-07-27 03:25:35.744</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="I145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:47.240</t>
+          <t>2026-07-27 03:25:35.914</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:47.410</t>
+          <t>2026-07-27 03:25:36.084</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:47.580</t>
+          <t>2026-07-27 03:25:36.254</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:47.750</t>
+          <t>2026-07-27 03:25:36.424</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:47.920</t>
+          <t>2026-07-27 03:25:36.594</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:48.090</t>
+          <t>2026-07-27 03:25:36.764</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="I151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:48.260</t>
+          <t>2026-07-27 03:25:36.934</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:48.430</t>
+          <t>2026-07-27 03:25:37.104</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:48.600</t>
+          <t>2026-07-27 03:25:37.274</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:48.770</t>
+          <t>2026-07-27 03:25:37.444</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:48.940</t>
+          <t>2026-07-27 03:25:37.614</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:49.110</t>
+          <t>2026-07-27 03:25:37.784</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="I157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:49.280</t>
+          <t>2026-07-27 03:25:37.954</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:49.450</t>
+          <t>2026-07-27 03:25:38.124</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="I159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:49.620</t>
+          <t>2026-07-27 03:25:38.294</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:49.790</t>
+          <t>2026-07-27 03:25:38.464</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:49.960</t>
+          <t>2026-07-27 03:25:38.634</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:50.130</t>
+          <t>2026-07-27 03:25:38.804</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="I163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:50.300</t>
+          <t>2026-07-27 03:25:38.974</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:50.470</t>
+          <t>2026-07-27 03:25:39.144</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="I165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:50.640</t>
+          <t>2026-07-27 03:25:39.314</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:50.810</t>
+          <t>2026-07-27 03:25:39.484</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="I167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:50.980</t>
+          <t>2026-07-27 03:25:39.654</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:51.150</t>
+          <t>2026-07-27 03:25:39.824</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="I169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:51.320</t>
+          <t>2026-07-27 03:25:39.994</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:51.490</t>
+          <t>2026-07-27 03:25:40.164</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="I171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:51.660</t>
+          <t>2026-07-27 03:25:40.334</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:51.830</t>
+          <t>2026-07-27 03:25:40.504</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:52.000</t>
+          <t>2026-07-27 03:25:40.674</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:52.170</t>
+          <t>2026-07-27 03:25:40.844</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:52.340</t>
+          <t>2026-07-27 03:25:41.014</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:52.510</t>
+          <t>2026-07-27 03:25:41.184</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="I177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:52.680</t>
+          <t>2026-07-27 03:25:41.354</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:52.850</t>
+          <t>2026-07-27 03:25:41.524</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="I179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:53.020</t>
+          <t>2026-07-27 03:25:41.694</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:53.190</t>
+          <t>2026-07-27 03:25:41.864</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:53.360</t>
+          <t>2026-07-27 03:25:42.034</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:53.530</t>
+          <t>2026-07-27 03:25:42.204</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:53.700</t>
+          <t>2026-07-27 03:25:42.374</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:53.870</t>
+          <t>2026-07-27 03:25:42.544</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="I185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:54.040</t>
+          <t>2026-07-27 03:25:42.714</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="I186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:54.210</t>
+          <t>2026-07-27 03:25:42.884</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="I187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:54.380</t>
+          <t>2026-07-27 03:25:43.054</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:54.550</t>
+          <t>2026-07-27 03:25:43.224</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:54.720</t>
+          <t>2026-07-27 03:25:43.394</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:54.890</t>
+          <t>2026-07-27 03:25:43.564</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="I191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:55.060</t>
+          <t>2026-07-27 03:25:43.734</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="I192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:55.230</t>
+          <t>2026-07-27 03:25:43.904</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="I193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:55.400</t>
+          <t>2026-07-27 03:25:44.074</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="I194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:55.570</t>
+          <t>2026-07-27 03:25:44.244</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="I195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:55.740</t>
+          <t>2026-07-27 03:25:44.414</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="I196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:55.910</t>
+          <t>2026-07-27 03:25:44.584</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="I197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:56.080</t>
+          <t>2026-07-27 03:25:44.754</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="I198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:56.250</t>
+          <t>2026-07-27 03:25:44.924</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="I199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:56.420</t>
+          <t>2026-07-27 03:25:45.094</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="I200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:56.590</t>
+          <t>2026-07-27 03:25:45.264</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:56.760</t>
+          <t>2026-07-27 03:25:45.434</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="I202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:56.930</t>
+          <t>2026-07-27 03:25:45.604</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="I203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:57.100</t>
+          <t>2026-07-27 03:25:45.774</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="I204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:57.270</t>
+          <t>2026-07-27 03:25:45.944</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="I205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:57.440</t>
+          <t>2026-07-27 03:25:46.114</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="I206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:57.610</t>
+          <t>2026-07-27 03:25:46.284</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="I207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:57.780</t>
+          <t>2026-07-27 03:25:46.454</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="I208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:57.950</t>
+          <t>2026-07-27 03:25:46.624</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="I209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:58.120</t>
+          <t>2026-07-27 03:25:46.794</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:58.290</t>
+          <t>2026-07-27 03:25:46.964</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="I211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:58.460</t>
+          <t>2026-07-27 03:25:47.134</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="I212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:58.630</t>
+          <t>2026-07-27 03:25:47.304</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="I213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:58.800</t>
+          <t>2026-07-27 03:25:47.474</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:58.970</t>
+          <t>2026-07-27 03:25:47.644</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="I215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:59.140</t>
+          <t>2026-07-27 03:25:47.814</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:59.310</t>
+          <t>2026-07-27 03:25:47.984</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="I217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:59.480</t>
+          <t>2026-07-27 03:25:48.154</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="I218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:59.650</t>
+          <t>2026-07-27 03:25:48.324</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="I219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:59.820</t>
+          <t>2026-07-27 03:25:48.494</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:53:59.990</t>
+          <t>2026-07-27 03:25:48.664</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="I221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:00.160</t>
+          <t>2026-07-27 03:25:48.834</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:00.330</t>
+          <t>2026-07-27 03:25:49.004</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="I223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:00.500</t>
+          <t>2026-07-27 03:25:49.174</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="I224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:00.670</t>
+          <t>2026-07-27 03:25:49.344</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="I225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:00.840</t>
+          <t>2026-07-27 03:25:49.514</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="I226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:01.010</t>
+          <t>2026-07-27 03:25:49.684</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="I227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:01.180</t>
+          <t>2026-07-27 03:25:49.854</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="I228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:01.350</t>
+          <t>2026-07-27 03:25:50.024</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="I229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:01.520</t>
+          <t>2026-07-27 03:25:50.194</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="I230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:01.690</t>
+          <t>2026-07-27 03:25:50.364</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="I231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:01.860</t>
+          <t>2026-07-27 03:25:50.534</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="I232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:02.030</t>
+          <t>2026-07-27 03:25:50.704</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:02.200</t>
+          <t>2026-07-27 03:25:50.874</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="I234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:02.370</t>
+          <t>2026-07-27 03:25:51.044</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="I235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:02.540</t>
+          <t>2026-07-27 03:25:51.214</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:02.710</t>
+          <t>2026-07-27 03:25:51.384</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="I237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:02.880</t>
+          <t>2026-07-27 03:25:51.554</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="I238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:03.050</t>
+          <t>2026-07-27 03:25:51.724</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="I239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:03.220</t>
+          <t>2026-07-27 03:25:51.894</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="I240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:03.390</t>
+          <t>2026-07-27 03:25:52.064</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:03.560</t>
+          <t>2026-07-27 03:25:52.234</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:03.730</t>
+          <t>2026-07-27 03:25:52.404</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="I243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:03.900</t>
+          <t>2026-07-27 03:25:52.574</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="I244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:04.070</t>
+          <t>2026-07-27 03:25:52.744</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="I245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:04.240</t>
+          <t>2026-07-27 03:25:52.914</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="I246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:04.410</t>
+          <t>2026-07-27 03:25:53.084</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="I247" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:04.580</t>
+          <t>2026-07-27 03:25:53.254</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="I248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:04.750</t>
+          <t>2026-07-27 03:25:53.424</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="I249" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:04.920</t>
+          <t>2026-07-27 03:25:53.594</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="I250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:05.090</t>
+          <t>2026-07-27 03:25:53.764</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I251" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:05.260</t>
+          <t>2026-07-27 03:25:53.934</t>
         </is>
       </c>
     </row>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="I252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:05.430</t>
+          <t>2026-07-27 03:25:54.104</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I253" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:05.600</t>
+          <t>2026-07-27 03:25:54.274</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="I254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:05.770</t>
+          <t>2026-07-27 03:25:54.444</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="I255" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:05.940</t>
+          <t>2026-07-27 03:25:54.614</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="I256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:06.110</t>
+          <t>2026-07-27 03:25:54.784</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="I257" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:06.280</t>
+          <t>2026-07-27 03:25:54.954</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:06.450</t>
+          <t>2026-07-27 03:25:55.124</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="I259" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:06.620</t>
+          <t>2026-07-27 03:25:55.294</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:06.790</t>
+          <t>2026-07-27 03:25:55.464</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="I261" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:06.960</t>
+          <t>2026-07-27 03:25:55.634</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="I262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:07.130</t>
+          <t>2026-07-27 03:25:55.804</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="I263" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:07.300</t>
+          <t>2026-07-27 03:25:55.974</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="I264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:07.470</t>
+          <t>2026-07-27 03:25:56.144</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="I265" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:07.640</t>
+          <t>2026-07-27 03:25:56.314</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="I266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:07.810</t>
+          <t>2026-07-27 03:25:56.484</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="I267" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:07.980</t>
+          <t>2026-07-27 03:25:56.654</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:08.150</t>
+          <t>2026-07-27 03:25:56.824</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="I269" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:08.320</t>
+          <t>2026-07-27 03:25:56.994</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="I270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:08.490</t>
+          <t>2026-07-27 03:25:57.164</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="I271" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:08.660</t>
+          <t>2026-07-27 03:25:57.334</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="I272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:08.830</t>
+          <t>2026-07-27 03:25:57.504</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="I273" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:09.000</t>
+          <t>2026-07-27 03:25:57.674</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="I274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:09.170</t>
+          <t>2026-07-27 03:25:57.844</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="I275" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:09.340</t>
+          <t>2026-07-27 03:25:58.014</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="I276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:09.510</t>
+          <t>2026-07-27 03:25:58.184</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="I277" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:09.680</t>
+          <t>2026-07-27 03:25:58.354</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="I278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:09.850</t>
+          <t>2026-07-27 03:25:58.524</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="I279" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:10.020</t>
+          <t>2026-07-27 03:25:58.694</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:10.190</t>
+          <t>2026-07-27 03:25:58.864</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="I281" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:10.360</t>
+          <t>2026-07-27 03:25:59.034</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="I282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:10.530</t>
+          <t>2026-07-27 03:25:59.204</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="I283" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:10.700</t>
+          <t>2026-07-27 03:25:59.374</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:10.870</t>
+          <t>2026-07-27 03:25:59.544</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="I285" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:11.040</t>
+          <t>2026-07-27 03:25:59.714</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:11.210</t>
+          <t>2026-07-27 03:25:59.884</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="I287" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:11.380</t>
+          <t>2026-07-27 03:26:00.054</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:11.550</t>
+          <t>2026-07-27 03:26:00.224</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="I289" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:11.720</t>
+          <t>2026-07-27 03:26:00.394</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:11.890</t>
+          <t>2026-07-27 03:26:00.564</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="I291" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:12.060</t>
+          <t>2026-07-27 03:26:00.734</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="I292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:12.230</t>
+          <t>2026-07-27 03:26:00.904</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="I293" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:12.400</t>
+          <t>2026-07-27 03:26:01.074</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="I294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:12.570</t>
+          <t>2026-07-27 03:26:01.244</t>
         </is>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="I295" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:12.740</t>
+          <t>2026-07-27 03:26:01.414</t>
         </is>
       </c>
     </row>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="I296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:12.910</t>
+          <t>2026-07-27 03:26:01.584</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="I297" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:13.080</t>
+          <t>2026-07-27 03:26:01.754</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="I298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:13.250</t>
+          <t>2026-07-27 03:26:01.924</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="I299" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:13.420</t>
+          <t>2026-07-27 03:26:02.094</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="I300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:13.590</t>
+          <t>2026-07-27 03:26:02.264</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="I301" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:13.760</t>
+          <t>2026-07-27 03:26:02.434</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="I302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:13.930</t>
+          <t>2026-07-27 03:26:02.604</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="I303" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:14.100</t>
+          <t>2026-07-27 03:26:02.774</t>
         </is>
       </c>
     </row>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="I304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:14.270</t>
+          <t>2026-07-27 03:26:02.944</t>
         </is>
       </c>
     </row>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="I305" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:14.440</t>
+          <t>2026-07-27 03:26:03.114</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="I306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:14.610</t>
+          <t>2026-07-27 03:26:03.284</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="I307" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:14.780</t>
+          <t>2026-07-27 03:26:03.454</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:14.950</t>
+          <t>2026-07-27 03:26:03.624</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="I309" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:15.120</t>
+          <t>2026-07-27 03:26:03.794</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="I310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:15.290</t>
+          <t>2026-07-27 03:26:03.964</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="I311" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:15.460</t>
+          <t>2026-07-27 03:26:04.134</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="I312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:15.630</t>
+          <t>2026-07-27 03:26:04.304</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="I313" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:15.800</t>
+          <t>2026-07-27 03:26:04.474</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="I314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:15.970</t>
+          <t>2026-07-27 03:26:04.644</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="I315" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:16.140</t>
+          <t>2026-07-27 03:26:04.814</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="I316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:16.310</t>
+          <t>2026-07-27 03:26:04.984</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="I317" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:16.480</t>
+          <t>2026-07-27 03:26:05.154</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="I318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:16.650</t>
+          <t>2026-07-27 03:26:05.324</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="I319" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:16.820</t>
+          <t>2026-07-27 03:26:05.494</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:16.990</t>
+          <t>2026-07-27 03:26:05.664</t>
         </is>
       </c>
     </row>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="I321" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:17.160</t>
+          <t>2026-07-27 03:26:05.834</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:17.330</t>
+          <t>2026-07-27 03:26:06.004</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="I323" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:17.500</t>
+          <t>2026-07-27 03:26:06.174</t>
         </is>
       </c>
     </row>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="I324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:17.670</t>
+          <t>2026-07-27 03:26:06.344</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="I325" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:17.840</t>
+          <t>2026-07-27 03:26:06.514</t>
         </is>
       </c>
     </row>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:18.010</t>
+          <t>2026-07-27 03:26:06.684</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="I327" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:18.180</t>
+          <t>2026-07-27 03:26:06.854</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:18.350</t>
+          <t>2026-07-27 03:26:07.024</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="I329" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:18.520</t>
+          <t>2026-07-27 03:26:07.194</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:18.690</t>
+          <t>2026-07-27 03:26:07.364</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="I331" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:18.860</t>
+          <t>2026-07-27 03:26:07.534</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:19.030</t>
+          <t>2026-07-27 03:26:07.704</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="I333" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:19.200</t>
+          <t>2026-07-27 03:26:07.874</t>
         </is>
       </c>
     </row>
@@ -14575,7 +14575,7 @@
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:19.370</t>
+          <t>2026-07-27 03:26:08.044</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="I335" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:19.540</t>
+          <t>2026-07-27 03:26:08.214</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:19.710</t>
+          <t>2026-07-27 03:26:08.384</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="I337" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:19.880</t>
+          <t>2026-07-27 03:26:08.554</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:20.050</t>
+          <t>2026-07-27 03:26:08.724</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="I339" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:20.220</t>
+          <t>2026-07-27 03:26:08.894</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:20.390</t>
+          <t>2026-07-27 03:26:09.064</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="I341" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:20.560</t>
+          <t>2026-07-27 03:26:09.234</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="I342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:20.730</t>
+          <t>2026-07-27 03:26:09.404</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="I343" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:20.900</t>
+          <t>2026-07-27 03:26:09.574</t>
         </is>
       </c>
     </row>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="I344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:21.070</t>
+          <t>2026-07-27 03:26:09.744</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="I345" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:21.240</t>
+          <t>2026-07-27 03:26:09.914</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:21.410</t>
+          <t>2026-07-27 03:26:10.084</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="I347" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:21.580</t>
+          <t>2026-07-27 03:26:10.254</t>
         </is>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="I348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:21.750</t>
+          <t>2026-07-27 03:26:10.424</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="I349" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:21.920</t>
+          <t>2026-07-27 03:26:10.594</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="I350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:22.090</t>
+          <t>2026-07-27 03:26:10.764</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="I351" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 08:54:22.260</t>
+          <t>2026-07-27 03:26:10.934</t>
         </is>
       </c>
     </row>

--- a/automated_test/load_report.xlsx
+++ b/automated_test/load_report.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:11</t>
+          <t>2026-07-27 03:38:43</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:11.604</t>
+          <t>2026-07-27 03:37:43.400</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:11.774</t>
+          <t>2026-07-27 03:37:43.570</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:11.944</t>
+          <t>2026-07-27 03:37:43.740</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:12.114</t>
+          <t>2026-07-27 03:37:43.910</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:12.284</t>
+          <t>2026-07-27 03:37:44.080</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:12.454</t>
+          <t>2026-07-27 03:37:44.250</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:12.624</t>
+          <t>2026-07-27 03:37:44.420</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:12.794</t>
+          <t>2026-07-27 03:37:44.590</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:12.964</t>
+          <t>2026-07-27 03:37:44.760</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:13.134</t>
+          <t>2026-07-27 03:37:44.930</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:13.304</t>
+          <t>2026-07-27 03:37:45.100</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:13.474</t>
+          <t>2026-07-27 03:37:45.270</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:13.644</t>
+          <t>2026-07-27 03:37:45.440</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:13.814</t>
+          <t>2026-07-27 03:37:45.610</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:13.984</t>
+          <t>2026-07-27 03:37:45.780</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:14.154</t>
+          <t>2026-07-27 03:37:45.950</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:14.324</t>
+          <t>2026-07-27 03:37:46.120</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:14.494</t>
+          <t>2026-07-27 03:37:46.290</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:14.664</t>
+          <t>2026-07-27 03:37:46.460</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:14.834</t>
+          <t>2026-07-27 03:37:46.630</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:15.004</t>
+          <t>2026-07-27 03:37:46.800</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:15.174</t>
+          <t>2026-07-27 03:37:46.970</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:15.344</t>
+          <t>2026-07-27 03:37:47.140</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:15.514</t>
+          <t>2026-07-27 03:37:47.310</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:15.684</t>
+          <t>2026-07-27 03:37:47.480</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:15.854</t>
+          <t>2026-07-27 03:37:47.650</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:16.024</t>
+          <t>2026-07-27 03:37:47.820</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:16.194</t>
+          <t>2026-07-27 03:37:47.990</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:16.364</t>
+          <t>2026-07-27 03:37:48.160</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:16.534</t>
+          <t>2026-07-27 03:37:48.330</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:16.704</t>
+          <t>2026-07-27 03:37:48.500</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:16.874</t>
+          <t>2026-07-27 03:37:48.670</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:17.044</t>
+          <t>2026-07-27 03:37:48.840</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:17.214</t>
+          <t>2026-07-27 03:37:49.010</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:17.384</t>
+          <t>2026-07-27 03:37:49.180</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:17.554</t>
+          <t>2026-07-27 03:37:49.350</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:17.724</t>
+          <t>2026-07-27 03:37:49.520</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:17.894</t>
+          <t>2026-07-27 03:37:49.690</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:18.064</t>
+          <t>2026-07-27 03:37:49.860</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:18.234</t>
+          <t>2026-07-27 03:37:50.030</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:18.404</t>
+          <t>2026-07-27 03:37:50.200</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:18.574</t>
+          <t>2026-07-27 03:37:50.370</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:18.744</t>
+          <t>2026-07-27 03:37:50.540</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:18.914</t>
+          <t>2026-07-27 03:37:50.710</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:19.084</t>
+          <t>2026-07-27 03:37:50.880</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:19.254</t>
+          <t>2026-07-27 03:37:51.050</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:19.424</t>
+          <t>2026-07-27 03:37:51.220</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:19.594</t>
+          <t>2026-07-27 03:37:51.390</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:19.764</t>
+          <t>2026-07-27 03:37:51.560</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:19.934</t>
+          <t>2026-07-27 03:37:51.730</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:20.104</t>
+          <t>2026-07-27 03:37:51.900</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:20.274</t>
+          <t>2026-07-27 03:37:52.070</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:20.444</t>
+          <t>2026-07-27 03:37:52.240</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:20.614</t>
+          <t>2026-07-27 03:37:52.410</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:20.784</t>
+          <t>2026-07-27 03:37:52.580</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:20.954</t>
+          <t>2026-07-27 03:37:52.750</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:21.124</t>
+          <t>2026-07-27 03:37:52.920</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:21.294</t>
+          <t>2026-07-27 03:37:53.090</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:21.464</t>
+          <t>2026-07-27 03:37:53.260</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:21.634</t>
+          <t>2026-07-27 03:37:53.430</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:21.804</t>
+          <t>2026-07-27 03:37:53.600</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:21.974</t>
+          <t>2026-07-27 03:37:53.770</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:22.144</t>
+          <t>2026-07-27 03:37:53.940</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:22.314</t>
+          <t>2026-07-27 03:37:54.110</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:22.484</t>
+          <t>2026-07-27 03:37:54.280</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:22.654</t>
+          <t>2026-07-27 03:37:54.450</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:22.824</t>
+          <t>2026-07-27 03:37:54.620</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:22.994</t>
+          <t>2026-07-27 03:37:54.790</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:23.164</t>
+          <t>2026-07-27 03:37:54.960</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:23.334</t>
+          <t>2026-07-27 03:37:55.130</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:23.504</t>
+          <t>2026-07-27 03:37:55.300</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:23.674</t>
+          <t>2026-07-27 03:37:55.470</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:23.844</t>
+          <t>2026-07-27 03:37:55.640</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:24.014</t>
+          <t>2026-07-27 03:37:55.810</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:24.184</t>
+          <t>2026-07-27 03:37:55.980</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:24.354</t>
+          <t>2026-07-27 03:37:56.150</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:24.524</t>
+          <t>2026-07-27 03:37:56.320</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:24.694</t>
+          <t>2026-07-27 03:37:56.490</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:24.864</t>
+          <t>2026-07-27 03:37:56.660</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:25.034</t>
+          <t>2026-07-27 03:37:56.830</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:25.204</t>
+          <t>2026-07-27 03:37:57.000</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:25.374</t>
+          <t>2026-07-27 03:37:57.170</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:25.544</t>
+          <t>2026-07-27 03:37:57.340</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:25.714</t>
+          <t>2026-07-27 03:37:57.510</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:25.884</t>
+          <t>2026-07-27 03:37:57.680</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:26.054</t>
+          <t>2026-07-27 03:37:57.850</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:26.224</t>
+          <t>2026-07-27 03:37:58.020</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:26.394</t>
+          <t>2026-07-27 03:37:58.190</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:26.564</t>
+          <t>2026-07-27 03:37:58.360</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:26.734</t>
+          <t>2026-07-27 03:37:58.530</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:26.904</t>
+          <t>2026-07-27 03:37:58.700</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:27.074</t>
+          <t>2026-07-27 03:37:58.870</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:27.244</t>
+          <t>2026-07-27 03:37:59.040</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:27.414</t>
+          <t>2026-07-27 03:37:59.210</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:27.584</t>
+          <t>2026-07-27 03:37:59.380</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:27.754</t>
+          <t>2026-07-27 03:37:59.550</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:27.924</t>
+          <t>2026-07-27 03:37:59.720</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:28.094</t>
+          <t>2026-07-27 03:37:59.890</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:28.264</t>
+          <t>2026-07-27 03:38:00.060</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:28.434</t>
+          <t>2026-07-27 03:38:00.230</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:28.604</t>
+          <t>2026-07-27 03:38:00.400</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:28.774</t>
+          <t>2026-07-27 03:38:00.570</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:28.944</t>
+          <t>2026-07-27 03:38:00.740</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:29.114</t>
+          <t>2026-07-27 03:38:00.910</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:29.284</t>
+          <t>2026-07-27 03:38:01.080</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:29.454</t>
+          <t>2026-07-27 03:38:01.250</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:29.624</t>
+          <t>2026-07-27 03:38:01.420</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:29.794</t>
+          <t>2026-07-27 03:38:01.590</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:29.964</t>
+          <t>2026-07-27 03:38:01.760</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:30.134</t>
+          <t>2026-07-27 03:38:01.930</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:30.304</t>
+          <t>2026-07-27 03:38:02.100</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:30.474</t>
+          <t>2026-07-27 03:38:02.270</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:30.644</t>
+          <t>2026-07-27 03:38:02.440</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:30.814</t>
+          <t>2026-07-27 03:38:02.610</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:30.984</t>
+          <t>2026-07-27 03:38:02.780</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:31.154</t>
+          <t>2026-07-27 03:38:02.950</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:31.324</t>
+          <t>2026-07-27 03:38:03.120</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:31.494</t>
+          <t>2026-07-27 03:38:03.290</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:31.664</t>
+          <t>2026-07-27 03:38:03.460</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:31.834</t>
+          <t>2026-07-27 03:38:03.630</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:32.004</t>
+          <t>2026-07-27 03:38:03.800</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:32.174</t>
+          <t>2026-07-27 03:38:03.970</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:32.344</t>
+          <t>2026-07-27 03:38:04.140</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:32.514</t>
+          <t>2026-07-27 03:38:04.310</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:32.684</t>
+          <t>2026-07-27 03:38:04.480</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:32.854</t>
+          <t>2026-07-27 03:38:04.650</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:33.024</t>
+          <t>2026-07-27 03:38:04.820</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:33.194</t>
+          <t>2026-07-27 03:38:04.990</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:33.364</t>
+          <t>2026-07-27 03:38:05.160</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:33.534</t>
+          <t>2026-07-27 03:38:05.330</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:33.704</t>
+          <t>2026-07-27 03:38:05.500</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:33.874</t>
+          <t>2026-07-27 03:38:05.670</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:34.044</t>
+          <t>2026-07-27 03:38:05.840</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:34.214</t>
+          <t>2026-07-27 03:38:06.010</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:34.384</t>
+          <t>2026-07-27 03:38:06.180</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="I137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:34.554</t>
+          <t>2026-07-27 03:38:06.350</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:34.724</t>
+          <t>2026-07-27 03:38:06.520</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:34.894</t>
+          <t>2026-07-27 03:38:06.690</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:35.064</t>
+          <t>2026-07-27 03:38:06.860</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="I141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:35.234</t>
+          <t>2026-07-27 03:38:07.030</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:35.404</t>
+          <t>2026-07-27 03:38:07.200</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:35.574</t>
+          <t>2026-07-27 03:38:07.370</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:35.744</t>
+          <t>2026-07-27 03:38:07.540</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="I145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:35.914</t>
+          <t>2026-07-27 03:38:07.710</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:36.084</t>
+          <t>2026-07-27 03:38:07.880</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:36.254</t>
+          <t>2026-07-27 03:38:08.050</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:36.424</t>
+          <t>2026-07-27 03:38:08.220</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:36.594</t>
+          <t>2026-07-27 03:38:08.390</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:36.764</t>
+          <t>2026-07-27 03:38:08.560</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="I151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:36.934</t>
+          <t>2026-07-27 03:38:08.730</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:37.104</t>
+          <t>2026-07-27 03:38:08.900</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:37.274</t>
+          <t>2026-07-27 03:38:09.070</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:37.444</t>
+          <t>2026-07-27 03:38:09.240</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:37.614</t>
+          <t>2026-07-27 03:38:09.410</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:37.784</t>
+          <t>2026-07-27 03:38:09.580</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="I157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:37.954</t>
+          <t>2026-07-27 03:38:09.750</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:38.124</t>
+          <t>2026-07-27 03:38:09.920</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="I159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:38.294</t>
+          <t>2026-07-27 03:38:10.090</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:38.464</t>
+          <t>2026-07-27 03:38:10.260</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:38.634</t>
+          <t>2026-07-27 03:38:10.430</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:38.804</t>
+          <t>2026-07-27 03:38:10.600</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="I163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:38.974</t>
+          <t>2026-07-27 03:38:10.770</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:39.144</t>
+          <t>2026-07-27 03:38:10.940</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="I165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:39.314</t>
+          <t>2026-07-27 03:38:11.110</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:39.484</t>
+          <t>2026-07-27 03:38:11.280</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="I167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:39.654</t>
+          <t>2026-07-27 03:38:11.450</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:39.824</t>
+          <t>2026-07-27 03:38:11.620</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="I169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:39.994</t>
+          <t>2026-07-27 03:38:11.790</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:40.164</t>
+          <t>2026-07-27 03:38:11.960</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="I171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:40.334</t>
+          <t>2026-07-27 03:38:12.130</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:40.504</t>
+          <t>2026-07-27 03:38:12.300</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:40.674</t>
+          <t>2026-07-27 03:38:12.470</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:40.844</t>
+          <t>2026-07-27 03:38:12.640</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:41.014</t>
+          <t>2026-07-27 03:38:12.810</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:41.184</t>
+          <t>2026-07-27 03:38:12.980</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="I177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:41.354</t>
+          <t>2026-07-27 03:38:13.150</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:41.524</t>
+          <t>2026-07-27 03:38:13.320</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="I179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:41.694</t>
+          <t>2026-07-27 03:38:13.490</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:41.864</t>
+          <t>2026-07-27 03:38:13.660</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:42.034</t>
+          <t>2026-07-27 03:38:13.830</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:42.204</t>
+          <t>2026-07-27 03:38:14.000</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:42.374</t>
+          <t>2026-07-27 03:38:14.170</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:42.544</t>
+          <t>2026-07-27 03:38:14.340</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="I185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:42.714</t>
+          <t>2026-07-27 03:38:14.510</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="I186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:42.884</t>
+          <t>2026-07-27 03:38:14.680</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="I187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:43.054</t>
+          <t>2026-07-27 03:38:14.850</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:43.224</t>
+          <t>2026-07-27 03:38:15.020</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:43.394</t>
+          <t>2026-07-27 03:38:15.190</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:43.564</t>
+          <t>2026-07-27 03:38:15.360</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="I191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:43.734</t>
+          <t>2026-07-27 03:38:15.530</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="I192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:43.904</t>
+          <t>2026-07-27 03:38:15.700</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="I193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:44.074</t>
+          <t>2026-07-27 03:38:15.870</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="I194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:44.244</t>
+          <t>2026-07-27 03:38:16.040</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="I195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:44.414</t>
+          <t>2026-07-27 03:38:16.210</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="I196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:44.584</t>
+          <t>2026-07-27 03:38:16.380</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="I197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:44.754</t>
+          <t>2026-07-27 03:38:16.550</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="I198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:44.924</t>
+          <t>2026-07-27 03:38:16.720</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="I199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:45.094</t>
+          <t>2026-07-27 03:38:16.890</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="I200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:45.264</t>
+          <t>2026-07-27 03:38:17.060</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:45.434</t>
+          <t>2026-07-27 03:38:17.230</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="I202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:45.604</t>
+          <t>2026-07-27 03:38:17.400</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="I203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:45.774</t>
+          <t>2026-07-27 03:38:17.570</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="I204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:45.944</t>
+          <t>2026-07-27 03:38:17.740</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="I205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:46.114</t>
+          <t>2026-07-27 03:38:17.910</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="I206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:46.284</t>
+          <t>2026-07-27 03:38:18.080</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="I207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:46.454</t>
+          <t>2026-07-27 03:38:18.250</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="I208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:46.624</t>
+          <t>2026-07-27 03:38:18.420</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="I209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:46.794</t>
+          <t>2026-07-27 03:38:18.590</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:46.964</t>
+          <t>2026-07-27 03:38:18.760</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="I211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:47.134</t>
+          <t>2026-07-27 03:38:18.930</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="I212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:47.304</t>
+          <t>2026-07-27 03:38:19.100</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="I213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:47.474</t>
+          <t>2026-07-27 03:38:19.270</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:47.644</t>
+          <t>2026-07-27 03:38:19.440</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="I215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:47.814</t>
+          <t>2026-07-27 03:38:19.610</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:47.984</t>
+          <t>2026-07-27 03:38:19.780</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="I217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:48.154</t>
+          <t>2026-07-27 03:38:19.950</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="I218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:48.324</t>
+          <t>2026-07-27 03:38:20.120</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="I219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:48.494</t>
+          <t>2026-07-27 03:38:20.290</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:48.664</t>
+          <t>2026-07-27 03:38:20.460</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="I221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:48.834</t>
+          <t>2026-07-27 03:38:20.630</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:49.004</t>
+          <t>2026-07-27 03:38:20.800</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="I223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:49.174</t>
+          <t>2026-07-27 03:38:20.970</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="I224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:49.344</t>
+          <t>2026-07-27 03:38:21.140</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="I225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:49.514</t>
+          <t>2026-07-27 03:38:21.310</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="I226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:49.684</t>
+          <t>2026-07-27 03:38:21.480</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="I227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:49.854</t>
+          <t>2026-07-27 03:38:21.650</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="I228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:50.024</t>
+          <t>2026-07-27 03:38:21.820</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="I229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:50.194</t>
+          <t>2026-07-27 03:38:21.990</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="I230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:50.364</t>
+          <t>2026-07-27 03:38:22.160</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="I231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:50.534</t>
+          <t>2026-07-27 03:38:22.330</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="I232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:50.704</t>
+          <t>2026-07-27 03:38:22.500</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:50.874</t>
+          <t>2026-07-27 03:38:22.670</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="I234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:51.044</t>
+          <t>2026-07-27 03:38:22.840</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="I235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:51.214</t>
+          <t>2026-07-27 03:38:23.010</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:51.384</t>
+          <t>2026-07-27 03:38:23.180</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="I237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:51.554</t>
+          <t>2026-07-27 03:38:23.350</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="I238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:51.724</t>
+          <t>2026-07-27 03:38:23.520</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="I239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:51.894</t>
+          <t>2026-07-27 03:38:23.690</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="I240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:52.064</t>
+          <t>2026-07-27 03:38:23.860</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:52.234</t>
+          <t>2026-07-27 03:38:24.030</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:52.404</t>
+          <t>2026-07-27 03:38:24.200</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="I243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:52.574</t>
+          <t>2026-07-27 03:38:24.370</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="I244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:52.744</t>
+          <t>2026-07-27 03:38:24.540</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="I245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:52.914</t>
+          <t>2026-07-27 03:38:24.710</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="I246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:53.084</t>
+          <t>2026-07-27 03:38:24.880</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="I247" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:53.254</t>
+          <t>2026-07-27 03:38:25.050</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="I248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:53.424</t>
+          <t>2026-07-27 03:38:25.220</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="I249" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:53.594</t>
+          <t>2026-07-27 03:38:25.390</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="I250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:53.764</t>
+          <t>2026-07-27 03:38:25.560</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I251" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:53.934</t>
+          <t>2026-07-27 03:38:25.730</t>
         </is>
       </c>
     </row>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="I252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:54.104</t>
+          <t>2026-07-27 03:38:25.900</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I253" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:54.274</t>
+          <t>2026-07-27 03:38:26.070</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="I254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:54.444</t>
+          <t>2026-07-27 03:38:26.240</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="I255" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:54.614</t>
+          <t>2026-07-27 03:38:26.410</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="I256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:54.784</t>
+          <t>2026-07-27 03:38:26.580</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="I257" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:54.954</t>
+          <t>2026-07-27 03:38:26.750</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:55.124</t>
+          <t>2026-07-27 03:38:26.920</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="I259" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:55.294</t>
+          <t>2026-07-27 03:38:27.090</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:55.464</t>
+          <t>2026-07-27 03:38:27.260</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="I261" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:55.634</t>
+          <t>2026-07-27 03:38:27.430</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="I262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:55.804</t>
+          <t>2026-07-27 03:38:27.600</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="I263" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:55.974</t>
+          <t>2026-07-27 03:38:27.770</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="I264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:56.144</t>
+          <t>2026-07-27 03:38:27.940</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="I265" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:56.314</t>
+          <t>2026-07-27 03:38:28.110</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="I266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:56.484</t>
+          <t>2026-07-27 03:38:28.280</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="I267" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:56.654</t>
+          <t>2026-07-27 03:38:28.450</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:56.824</t>
+          <t>2026-07-27 03:38:28.620</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="I269" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:56.994</t>
+          <t>2026-07-27 03:38:28.790</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="I270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:57.164</t>
+          <t>2026-07-27 03:38:28.960</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="I271" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:57.334</t>
+          <t>2026-07-27 03:38:29.130</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="I272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:57.504</t>
+          <t>2026-07-27 03:38:29.300</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="I273" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:57.674</t>
+          <t>2026-07-27 03:38:29.470</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="I274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:57.844</t>
+          <t>2026-07-27 03:38:29.640</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="I275" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:58.014</t>
+          <t>2026-07-27 03:38:29.810</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="I276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:58.184</t>
+          <t>2026-07-27 03:38:29.980</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="I277" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:58.354</t>
+          <t>2026-07-27 03:38:30.150</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="I278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:58.524</t>
+          <t>2026-07-27 03:38:30.320</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="I279" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:58.694</t>
+          <t>2026-07-27 03:38:30.490</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:58.864</t>
+          <t>2026-07-27 03:38:30.660</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="I281" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:59.034</t>
+          <t>2026-07-27 03:38:30.830</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="I282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:59.204</t>
+          <t>2026-07-27 03:38:31.000</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="I283" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:59.374</t>
+          <t>2026-07-27 03:38:31.170</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:59.544</t>
+          <t>2026-07-27 03:38:31.340</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="I285" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:59.714</t>
+          <t>2026-07-27 03:38:31.510</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:25:59.884</t>
+          <t>2026-07-27 03:38:31.680</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="I287" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:00.054</t>
+          <t>2026-07-27 03:38:31.850</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:00.224</t>
+          <t>2026-07-27 03:38:32.020</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="I289" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:00.394</t>
+          <t>2026-07-27 03:38:32.190</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:00.564</t>
+          <t>2026-07-27 03:38:32.360</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="I291" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:00.734</t>
+          <t>2026-07-27 03:38:32.530</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="I292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:00.904</t>
+          <t>2026-07-27 03:38:32.700</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="I293" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:01.074</t>
+          <t>2026-07-27 03:38:32.870</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="I294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:01.244</t>
+          <t>2026-07-27 03:38:33.040</t>
         </is>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="I295" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:01.414</t>
+          <t>2026-07-27 03:38:33.210</t>
         </is>
       </c>
     </row>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="I296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:01.584</t>
+          <t>2026-07-27 03:38:33.380</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="I297" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:01.754</t>
+          <t>2026-07-27 03:38:33.550</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="I298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:01.924</t>
+          <t>2026-07-27 03:38:33.720</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="I299" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:02.094</t>
+          <t>2026-07-27 03:38:33.890</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="I300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:02.264</t>
+          <t>2026-07-27 03:38:34.060</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="I301" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:02.434</t>
+          <t>2026-07-27 03:38:34.230</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="I302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:02.604</t>
+          <t>2026-07-27 03:38:34.400</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="I303" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:02.774</t>
+          <t>2026-07-27 03:38:34.570</t>
         </is>
       </c>
     </row>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="I304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:02.944</t>
+          <t>2026-07-27 03:38:34.740</t>
         </is>
       </c>
     </row>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="I305" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:03.114</t>
+          <t>2026-07-27 03:38:34.910</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="I306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:03.284</t>
+          <t>2026-07-27 03:38:35.080</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="I307" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:03.454</t>
+          <t>2026-07-27 03:38:35.250</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:03.624</t>
+          <t>2026-07-27 03:38:35.420</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="I309" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:03.794</t>
+          <t>2026-07-27 03:38:35.590</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="I310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:03.964</t>
+          <t>2026-07-27 03:38:35.760</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="I311" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:04.134</t>
+          <t>2026-07-27 03:38:35.930</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="I312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:04.304</t>
+          <t>2026-07-27 03:38:36.100</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="I313" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:04.474</t>
+          <t>2026-07-27 03:38:36.270</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="I314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:04.644</t>
+          <t>2026-07-27 03:38:36.440</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="I315" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:04.814</t>
+          <t>2026-07-27 03:38:36.610</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="I316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:04.984</t>
+          <t>2026-07-27 03:38:36.780</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="I317" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:05.154</t>
+          <t>2026-07-27 03:38:36.950</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="I318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:05.324</t>
+          <t>2026-07-27 03:38:37.120</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="I319" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:05.494</t>
+          <t>2026-07-27 03:38:37.290</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:05.664</t>
+          <t>2026-07-27 03:38:37.460</t>
         </is>
       </c>
     </row>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="I321" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:05.834</t>
+          <t>2026-07-27 03:38:37.630</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:06.004</t>
+          <t>2026-07-27 03:38:37.800</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="I323" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:06.174</t>
+          <t>2026-07-27 03:38:37.970</t>
         </is>
       </c>
     </row>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="I324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:06.344</t>
+          <t>2026-07-27 03:38:38.140</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="I325" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:06.514</t>
+          <t>2026-07-27 03:38:38.310</t>
         </is>
       </c>
     </row>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:06.684</t>
+          <t>2026-07-27 03:38:38.480</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="I327" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:06.854</t>
+          <t>2026-07-27 03:38:38.650</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:07.024</t>
+          <t>2026-07-27 03:38:38.820</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="I329" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:07.194</t>
+          <t>2026-07-27 03:38:38.990</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:07.364</t>
+          <t>2026-07-27 03:38:39.160</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="I331" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:07.534</t>
+          <t>2026-07-27 03:38:39.330</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:07.704</t>
+          <t>2026-07-27 03:38:39.500</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="I333" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:07.874</t>
+          <t>2026-07-27 03:38:39.670</t>
         </is>
       </c>
     </row>
@@ -14575,7 +14575,7 @@
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:08.044</t>
+          <t>2026-07-27 03:38:39.840</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="I335" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:08.214</t>
+          <t>2026-07-27 03:38:40.010</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:08.384</t>
+          <t>2026-07-27 03:38:40.180</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="I337" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:08.554</t>
+          <t>2026-07-27 03:38:40.350</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:08.724</t>
+          <t>2026-07-27 03:38:40.520</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="I339" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:08.894</t>
+          <t>2026-07-27 03:38:40.690</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:09.064</t>
+          <t>2026-07-27 03:38:40.860</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="I341" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:09.234</t>
+          <t>2026-07-27 03:38:41.030</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="I342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:09.404</t>
+          <t>2026-07-27 03:38:41.200</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="I343" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:09.574</t>
+          <t>2026-07-27 03:38:41.370</t>
         </is>
       </c>
     </row>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="I344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:09.744</t>
+          <t>2026-07-27 03:38:41.540</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="I345" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:09.914</t>
+          <t>2026-07-27 03:38:41.710</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:10.084</t>
+          <t>2026-07-27 03:38:41.880</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="I347" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:10.254</t>
+          <t>2026-07-27 03:38:42.050</t>
         </is>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="I348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:10.424</t>
+          <t>2026-07-27 03:38:42.220</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="I349" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:10.594</t>
+          <t>2026-07-27 03:38:42.390</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="I350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:10.764</t>
+          <t>2026-07-27 03:38:42.560</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="I351" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:26:10.934</t>
+          <t>2026-07-27 03:38:42.730</t>
         </is>
       </c>
     </row>

--- a/automated_test/load_report.xlsx
+++ b/automated_test/load_report.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:43</t>
+          <t>2026-08-07 07:48:59</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:43.400</t>
+          <t>2026-08-07 07:47:59.420</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:43.570</t>
+          <t>2026-08-07 07:47:59.590</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:43.740</t>
+          <t>2026-08-07 07:47:59.760</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:43.910</t>
+          <t>2026-08-07 07:47:59.930</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:44.080</t>
+          <t>2026-08-07 07:48:00.100</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:44.250</t>
+          <t>2026-08-07 07:48:00.270</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:44.420</t>
+          <t>2026-08-07 07:48:00.440</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:44.590</t>
+          <t>2026-08-07 07:48:00.610</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:44.760</t>
+          <t>2026-08-07 07:48:00.780</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:44.930</t>
+          <t>2026-08-07 07:48:00.950</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:45.100</t>
+          <t>2026-08-07 07:48:01.120</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:45.270</t>
+          <t>2026-08-07 07:48:01.290</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:45.440</t>
+          <t>2026-08-07 07:48:01.460</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:45.610</t>
+          <t>2026-08-07 07:48:01.630</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:45.780</t>
+          <t>2026-08-07 07:48:01.800</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:45.950</t>
+          <t>2026-08-07 07:48:01.970</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:46.120</t>
+          <t>2026-08-07 07:48:02.140</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:46.290</t>
+          <t>2026-08-07 07:48:02.310</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:46.460</t>
+          <t>2026-08-07 07:48:02.480</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:46.630</t>
+          <t>2026-08-07 07:48:02.650</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:46.800</t>
+          <t>2026-08-07 07:48:02.820</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:46.970</t>
+          <t>2026-08-07 07:48:02.990</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:47.140</t>
+          <t>2026-08-07 07:48:03.160</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:47.310</t>
+          <t>2026-08-07 07:48:03.330</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:47.480</t>
+          <t>2026-08-07 07:48:03.500</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:47.650</t>
+          <t>2026-08-07 07:48:03.670</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:47.820</t>
+          <t>2026-08-07 07:48:03.840</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:47.990</t>
+          <t>2026-08-07 07:48:04.010</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:48.160</t>
+          <t>2026-08-07 07:48:04.180</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:48.330</t>
+          <t>2026-08-07 07:48:04.350</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:48.500</t>
+          <t>2026-08-07 07:48:04.520</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:48.670</t>
+          <t>2026-08-07 07:48:04.690</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:48.840</t>
+          <t>2026-08-07 07:48:04.860</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:49.010</t>
+          <t>2026-08-07 07:48:05.030</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:49.180</t>
+          <t>2026-08-07 07:48:05.200</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:49.350</t>
+          <t>2026-08-07 07:48:05.370</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:49.520</t>
+          <t>2026-08-07 07:48:05.540</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:49.690</t>
+          <t>2026-08-07 07:48:05.710</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:49.860</t>
+          <t>2026-08-07 07:48:05.880</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:50.030</t>
+          <t>2026-08-07 07:48:06.050</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:50.200</t>
+          <t>2026-08-07 07:48:06.220</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:50.370</t>
+          <t>2026-08-07 07:48:06.390</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:50.540</t>
+          <t>2026-08-07 07:48:06.560</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:50.710</t>
+          <t>2026-08-07 07:48:06.730</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:50.880</t>
+          <t>2026-08-07 07:48:06.900</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:51.050</t>
+          <t>2026-08-07 07:48:07.070</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:51.220</t>
+          <t>2026-08-07 07:48:07.240</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:51.390</t>
+          <t>2026-08-07 07:48:07.410</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:51.560</t>
+          <t>2026-08-07 07:48:07.580</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:51.730</t>
+          <t>2026-08-07 07:48:07.750</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:51.900</t>
+          <t>2026-08-07 07:48:07.920</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:52.070</t>
+          <t>2026-08-07 07:48:08.090</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:52.240</t>
+          <t>2026-08-07 07:48:08.260</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:52.410</t>
+          <t>2026-08-07 07:48:08.430</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:52.580</t>
+          <t>2026-08-07 07:48:08.600</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:52.750</t>
+          <t>2026-08-07 07:48:08.770</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:52.920</t>
+          <t>2026-08-07 07:48:08.940</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:53.090</t>
+          <t>2026-08-07 07:48:09.110</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:53.260</t>
+          <t>2026-08-07 07:48:09.280</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:53.430</t>
+          <t>2026-08-07 07:48:09.450</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:53.600</t>
+          <t>2026-08-07 07:48:09.620</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:53.770</t>
+          <t>2026-08-07 07:48:09.790</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:53.940</t>
+          <t>2026-08-07 07:48:09.960</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:54.110</t>
+          <t>2026-08-07 07:48:10.130</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:54.280</t>
+          <t>2026-08-07 07:48:10.300</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:54.450</t>
+          <t>2026-08-07 07:48:10.470</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:54.620</t>
+          <t>2026-08-07 07:48:10.640</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:54.790</t>
+          <t>2026-08-07 07:48:10.810</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:54.960</t>
+          <t>2026-08-07 07:48:10.980</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:55.130</t>
+          <t>2026-08-07 07:48:11.150</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:55.300</t>
+          <t>2026-08-07 07:48:11.320</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:55.470</t>
+          <t>2026-08-07 07:48:11.490</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:55.640</t>
+          <t>2026-08-07 07:48:11.660</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:55.810</t>
+          <t>2026-08-07 07:48:11.830</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:55.980</t>
+          <t>2026-08-07 07:48:12.000</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:56.150</t>
+          <t>2026-08-07 07:48:12.170</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:56.320</t>
+          <t>2026-08-07 07:48:12.340</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:56.490</t>
+          <t>2026-08-07 07:48:12.510</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:56.660</t>
+          <t>2026-08-07 07:48:12.680</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:56.830</t>
+          <t>2026-08-07 07:48:12.850</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:57.000</t>
+          <t>2026-08-07 07:48:13.020</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:57.170</t>
+          <t>2026-08-07 07:48:13.190</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:57.340</t>
+          <t>2026-08-07 07:48:13.360</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:57.510</t>
+          <t>2026-08-07 07:48:13.530</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:57.680</t>
+          <t>2026-08-07 07:48:13.700</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:57.850</t>
+          <t>2026-08-07 07:48:13.870</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:58.020</t>
+          <t>2026-08-07 07:48:14.040</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:58.190</t>
+          <t>2026-08-07 07:48:14.210</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:58.360</t>
+          <t>2026-08-07 07:48:14.380</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:58.530</t>
+          <t>2026-08-07 07:48:14.550</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:58.700</t>
+          <t>2026-08-07 07:48:14.720</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:58.870</t>
+          <t>2026-08-07 07:48:14.890</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:59.040</t>
+          <t>2026-08-07 07:48:15.060</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:59.210</t>
+          <t>2026-08-07 07:48:15.230</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:59.380</t>
+          <t>2026-08-07 07:48:15.400</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:59.550</t>
+          <t>2026-08-07 07:48:15.570</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:59.720</t>
+          <t>2026-08-07 07:48:15.740</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:37:59.890</t>
+          <t>2026-08-07 07:48:15.910</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:00.060</t>
+          <t>2026-08-07 07:48:16.080</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:00.230</t>
+          <t>2026-08-07 07:48:16.250</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:00.400</t>
+          <t>2026-08-07 07:48:16.420</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:00.570</t>
+          <t>2026-08-07 07:48:16.590</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:00.740</t>
+          <t>2026-08-07 07:48:16.760</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:00.910</t>
+          <t>2026-08-07 07:48:16.930</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:01.080</t>
+          <t>2026-08-07 07:48:17.100</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:01.250</t>
+          <t>2026-08-07 07:48:17.270</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:01.420</t>
+          <t>2026-08-07 07:48:17.440</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:01.590</t>
+          <t>2026-08-07 07:48:17.610</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5391,7 @@
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:01.760</t>
+          <t>2026-08-07 07:48:17.780</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:01.930</t>
+          <t>2026-08-07 07:48:17.950</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:02.100</t>
+          <t>2026-08-07 07:48:18.120</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:02.270</t>
+          <t>2026-08-07 07:48:18.290</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:02.440</t>
+          <t>2026-08-07 07:48:18.460</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:02.610</t>
+          <t>2026-08-07 07:48:18.630</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:02.780</t>
+          <t>2026-08-07 07:48:18.800</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:02.950</t>
+          <t>2026-08-07 07:48:18.970</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:03.120</t>
+          <t>2026-08-07 07:48:19.140</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:03.290</t>
+          <t>2026-08-07 07:48:19.310</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:03.460</t>
+          <t>2026-08-07 07:48:19.480</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:03.630</t>
+          <t>2026-08-07 07:48:19.650</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:03.800</t>
+          <t>2026-08-07 07:48:19.820</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:03.970</t>
+          <t>2026-08-07 07:48:19.990</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:04.140</t>
+          <t>2026-08-07 07:48:20.160</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:04.310</t>
+          <t>2026-08-07 07:48:20.330</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:04.480</t>
+          <t>2026-08-07 07:48:20.500</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:04.650</t>
+          <t>2026-08-07 07:48:20.670</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:04.820</t>
+          <t>2026-08-07 07:48:20.840</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:04.990</t>
+          <t>2026-08-07 07:48:21.010</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:05.160</t>
+          <t>2026-08-07 07:48:21.180</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:05.330</t>
+          <t>2026-08-07 07:48:21.350</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:05.500</t>
+          <t>2026-08-07 07:48:21.520</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:05.670</t>
+          <t>2026-08-07 07:48:21.690</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:05.840</t>
+          <t>2026-08-07 07:48:21.860</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:06.010</t>
+          <t>2026-08-07 07:48:22.030</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:06.180</t>
+          <t>2026-08-07 07:48:22.200</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="I137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:06.350</t>
+          <t>2026-08-07 07:48:22.370</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:06.520</t>
+          <t>2026-08-07 07:48:22.540</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:06.690</t>
+          <t>2026-08-07 07:48:22.710</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:06.860</t>
+          <t>2026-08-07 07:48:22.880</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="I141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:07.030</t>
+          <t>2026-08-07 07:48:23.050</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:07.200</t>
+          <t>2026-08-07 07:48:23.220</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:07.370</t>
+          <t>2026-08-07 07:48:23.390</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:07.540</t>
+          <t>2026-08-07 07:48:23.560</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="I145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:07.710</t>
+          <t>2026-08-07 07:48:23.730</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:07.880</t>
+          <t>2026-08-07 07:48:23.900</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="I147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:08.050</t>
+          <t>2026-08-07 07:48:24.070</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:08.220</t>
+          <t>2026-08-07 07:48:24.240</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:08.390</t>
+          <t>2026-08-07 07:48:24.410</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:08.560</t>
+          <t>2026-08-07 07:48:24.580</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="I151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:08.730</t>
+          <t>2026-08-07 07:48:24.750</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:08.900</t>
+          <t>2026-08-07 07:48:24.920</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:09.070</t>
+          <t>2026-08-07 07:48:25.090</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:09.240</t>
+          <t>2026-08-07 07:48:25.260</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:09.410</t>
+          <t>2026-08-07 07:48:25.430</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:09.580</t>
+          <t>2026-08-07 07:48:25.600</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="I157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:09.750</t>
+          <t>2026-08-07 07:48:25.770</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:09.920</t>
+          <t>2026-08-07 07:48:25.940</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="I159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:10.090</t>
+          <t>2026-08-07 07:48:26.110</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:10.260</t>
+          <t>2026-08-07 07:48:26.280</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="I161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:10.430</t>
+          <t>2026-08-07 07:48:26.450</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:10.600</t>
+          <t>2026-08-07 07:48:26.620</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="I163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:10.770</t>
+          <t>2026-08-07 07:48:26.790</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:10.940</t>
+          <t>2026-08-07 07:48:26.960</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="I165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:11.110</t>
+          <t>2026-08-07 07:48:27.130</t>
         </is>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:11.280</t>
+          <t>2026-08-07 07:48:27.300</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="I167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:11.450</t>
+          <t>2026-08-07 07:48:27.470</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:11.620</t>
+          <t>2026-08-07 07:48:27.640</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="I169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:11.790</t>
+          <t>2026-08-07 07:48:27.810</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:11.960</t>
+          <t>2026-08-07 07:48:27.980</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="I171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:12.130</t>
+          <t>2026-08-07 07:48:28.150</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:12.300</t>
+          <t>2026-08-07 07:48:28.320</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:12.470</t>
+          <t>2026-08-07 07:48:28.490</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:12.640</t>
+          <t>2026-08-07 07:48:28.660</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:12.810</t>
+          <t>2026-08-07 07:48:28.830</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:12.980</t>
+          <t>2026-08-07 07:48:29.000</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="I177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:13.150</t>
+          <t>2026-08-07 07:48:29.170</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:13.320</t>
+          <t>2026-08-07 07:48:29.340</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="I179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:13.490</t>
+          <t>2026-08-07 07:48:29.510</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:13.660</t>
+          <t>2026-08-07 07:48:29.680</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:13.830</t>
+          <t>2026-08-07 07:48:29.850</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:14.000</t>
+          <t>2026-08-07 07:48:30.020</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="I183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:14.170</t>
+          <t>2026-08-07 07:48:30.190</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:14.340</t>
+          <t>2026-08-07 07:48:30.360</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="I185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:14.510</t>
+          <t>2026-08-07 07:48:30.530</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="I186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:14.680</t>
+          <t>2026-08-07 07:48:30.700</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8548,7 @@
       </c>
       <c r="I187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:14.850</t>
+          <t>2026-08-07 07:48:30.870</t>
         </is>
       </c>
     </row>
@@ -8589,7 +8589,7 @@
       </c>
       <c r="I188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:15.020</t>
+          <t>2026-08-07 07:48:31.040</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="I189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:15.190</t>
+          <t>2026-08-07 07:48:31.210</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="I190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:15.360</t>
+          <t>2026-08-07 07:48:31.380</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="I191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:15.530</t>
+          <t>2026-08-07 07:48:31.550</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="I192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:15.700</t>
+          <t>2026-08-07 07:48:31.720</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="I193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:15.870</t>
+          <t>2026-08-07 07:48:31.890</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="I194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:16.040</t>
+          <t>2026-08-07 07:48:32.060</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="I195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:16.210</t>
+          <t>2026-08-07 07:48:32.230</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="I196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:16.380</t>
+          <t>2026-08-07 07:48:32.400</t>
         </is>
       </c>
     </row>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="I197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:16.550</t>
+          <t>2026-08-07 07:48:32.570</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="I198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:16.720</t>
+          <t>2026-08-07 07:48:32.740</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="I199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:16.890</t>
+          <t>2026-08-07 07:48:32.910</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="I200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:17.060</t>
+          <t>2026-08-07 07:48:33.080</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:17.230</t>
+          <t>2026-08-07 07:48:33.250</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="I202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:17.400</t>
+          <t>2026-08-07 07:48:33.420</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="I203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:17.570</t>
+          <t>2026-08-07 07:48:33.590</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="I204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:17.740</t>
+          <t>2026-08-07 07:48:33.760</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="I205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:17.910</t>
+          <t>2026-08-07 07:48:33.930</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="I206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:18.080</t>
+          <t>2026-08-07 07:48:34.100</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="I207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:18.250</t>
+          <t>2026-08-07 07:48:34.270</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="I208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:18.420</t>
+          <t>2026-08-07 07:48:34.440</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="I209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:18.590</t>
+          <t>2026-08-07 07:48:34.610</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="I210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:18.760</t>
+          <t>2026-08-07 07:48:34.780</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="I211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:18.930</t>
+          <t>2026-08-07 07:48:34.950</t>
         </is>
       </c>
     </row>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="I212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:19.100</t>
+          <t>2026-08-07 07:48:35.120</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="I213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:19.270</t>
+          <t>2026-08-07 07:48:35.290</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:19.440</t>
+          <t>2026-08-07 07:48:35.460</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="I215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:19.610</t>
+          <t>2026-08-07 07:48:35.630</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:19.780</t>
+          <t>2026-08-07 07:48:35.800</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="I217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:19.950</t>
+          <t>2026-08-07 07:48:35.970</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="I218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:20.120</t>
+          <t>2026-08-07 07:48:36.140</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="I219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:20.290</t>
+          <t>2026-08-07 07:48:36.310</t>
         </is>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:20.460</t>
+          <t>2026-08-07 07:48:36.480</t>
         </is>
       </c>
     </row>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="I221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:20.630</t>
+          <t>2026-08-07 07:48:36.650</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:20.800</t>
+          <t>2026-08-07 07:48:36.820</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="I223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:20.970</t>
+          <t>2026-08-07 07:48:36.990</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="I224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:21.140</t>
+          <t>2026-08-07 07:48:37.160</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="I225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:21.310</t>
+          <t>2026-08-07 07:48:37.330</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="I226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:21.480</t>
+          <t>2026-08-07 07:48:37.500</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="I227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:21.650</t>
+          <t>2026-08-07 07:48:37.670</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
       </c>
       <c r="I228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:21.820</t>
+          <t>2026-08-07 07:48:37.840</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="I229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:21.990</t>
+          <t>2026-08-07 07:48:38.010</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="I230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:22.160</t>
+          <t>2026-08-07 07:48:38.180</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="I231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:22.330</t>
+          <t>2026-08-07 07:48:38.350</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="I232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:22.500</t>
+          <t>2026-08-07 07:48:38.520</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:22.670</t>
+          <t>2026-08-07 07:48:38.690</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="I234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:22.840</t>
+          <t>2026-08-07 07:48:38.860</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="I235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:23.010</t>
+          <t>2026-08-07 07:48:39.030</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:23.180</t>
+          <t>2026-08-07 07:48:39.200</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="I237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:23.350</t>
+          <t>2026-08-07 07:48:39.370</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="I238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:23.520</t>
+          <t>2026-08-07 07:48:39.540</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10680,7 @@
       </c>
       <c r="I239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:23.690</t>
+          <t>2026-08-07 07:48:39.710</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="I240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:23.860</t>
+          <t>2026-08-07 07:48:39.880</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:24.030</t>
+          <t>2026-08-07 07:48:40.050</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:24.200</t>
+          <t>2026-08-07 07:48:40.220</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="I243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:24.370</t>
+          <t>2026-08-07 07:48:40.390</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="I244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:24.540</t>
+          <t>2026-08-07 07:48:40.560</t>
         </is>
       </c>
     </row>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="I245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:24.710</t>
+          <t>2026-08-07 07:48:40.730</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="I246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:24.880</t>
+          <t>2026-08-07 07:48:40.900</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="I247" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:25.050</t>
+          <t>2026-08-07 07:48:41.070</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="I248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:25.220</t>
+          <t>2026-08-07 07:48:41.240</t>
         </is>
       </c>
     </row>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="I249" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:25.390</t>
+          <t>2026-08-07 07:48:41.410</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="I250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:25.560</t>
+          <t>2026-08-07 07:48:41.580</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I251" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:25.730</t>
+          <t>2026-08-07 07:48:41.750</t>
         </is>
       </c>
     </row>
@@ -11213,7 +11213,7 @@
       </c>
       <c r="I252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:25.900</t>
+          <t>2026-08-07 07:48:41.920</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="I253" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:26.070</t>
+          <t>2026-08-07 07:48:42.090</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="I254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:26.240</t>
+          <t>2026-08-07 07:48:42.260</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="I255" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:26.410</t>
+          <t>2026-08-07 07:48:42.430</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="I256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:26.580</t>
+          <t>2026-08-07 07:48:42.600</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="I257" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:26.750</t>
+          <t>2026-08-07 07:48:42.770</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:26.920</t>
+          <t>2026-08-07 07:48:42.940</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="I259" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:27.090</t>
+          <t>2026-08-07 07:48:43.110</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="I260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:27.260</t>
+          <t>2026-08-07 07:48:43.280</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="I261" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:27.430</t>
+          <t>2026-08-07 07:48:43.450</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="I262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:27.600</t>
+          <t>2026-08-07 07:48:43.620</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="I263" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:27.770</t>
+          <t>2026-08-07 07:48:43.790</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="I264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:27.940</t>
+          <t>2026-08-07 07:48:43.960</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="I265" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:28.110</t>
+          <t>2026-08-07 07:48:44.130</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="I266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:28.280</t>
+          <t>2026-08-07 07:48:44.300</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="I267" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:28.450</t>
+          <t>2026-08-07 07:48:44.470</t>
         </is>
       </c>
     </row>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:28.620</t>
+          <t>2026-08-07 07:48:44.640</t>
         </is>
       </c>
     </row>
@@ -11910,7 +11910,7 @@
       </c>
       <c r="I269" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:28.790</t>
+          <t>2026-08-07 07:48:44.810</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="I270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:28.960</t>
+          <t>2026-08-07 07:48:44.980</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="I271" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:29.130</t>
+          <t>2026-08-07 07:48:45.150</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="I272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:29.300</t>
+          <t>2026-08-07 07:48:45.320</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="I273" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:29.470</t>
+          <t>2026-08-07 07:48:45.490</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="I274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:29.640</t>
+          <t>2026-08-07 07:48:45.660</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="I275" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:29.810</t>
+          <t>2026-08-07 07:48:45.830</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="I276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:29.980</t>
+          <t>2026-08-07 07:48:46.000</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="I277" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:30.150</t>
+          <t>2026-08-07 07:48:46.170</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="I278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:30.320</t>
+          <t>2026-08-07 07:48:46.340</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="I279" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:30.490</t>
+          <t>2026-08-07 07:48:46.510</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:30.660</t>
+          <t>2026-08-07 07:48:46.680</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="I281" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:30.830</t>
+          <t>2026-08-07 07:48:46.850</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="I282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:31.000</t>
+          <t>2026-08-07 07:48:47.020</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="I283" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:31.170</t>
+          <t>2026-08-07 07:48:47.190</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:31.340</t>
+          <t>2026-08-07 07:48:47.360</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="I285" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:31.510</t>
+          <t>2026-08-07 07:48:47.530</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:31.680</t>
+          <t>2026-08-07 07:48:47.700</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="I287" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:31.850</t>
+          <t>2026-08-07 07:48:47.870</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:32.020</t>
+          <t>2026-08-07 07:48:48.040</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="I289" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:32.190</t>
+          <t>2026-08-07 07:48:48.210</t>
         </is>
       </c>
     </row>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:32.360</t>
+          <t>2026-08-07 07:48:48.380</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="I291" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:32.530</t>
+          <t>2026-08-07 07:48:48.550</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="I292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:32.700</t>
+          <t>2026-08-07 07:48:48.720</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="I293" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:32.870</t>
+          <t>2026-08-07 07:48:48.890</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="I294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:33.040</t>
+          <t>2026-08-07 07:48:49.060</t>
         </is>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       </c>
       <c r="I295" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:33.210</t>
+          <t>2026-08-07 07:48:49.230</t>
         </is>
       </c>
     </row>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="I296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:33.380</t>
+          <t>2026-08-07 07:48:49.400</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="I297" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:33.550</t>
+          <t>2026-08-07 07:48:49.570</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="I298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:33.720</t>
+          <t>2026-08-07 07:48:49.740</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="I299" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:33.890</t>
+          <t>2026-08-07 07:48:49.910</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="I300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:34.060</t>
+          <t>2026-08-07 07:48:50.080</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="I301" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:34.230</t>
+          <t>2026-08-07 07:48:50.250</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="I302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:34.400</t>
+          <t>2026-08-07 07:48:50.420</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="I303" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:34.570</t>
+          <t>2026-08-07 07:48:50.590</t>
         </is>
       </c>
     </row>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="I304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:34.740</t>
+          <t>2026-08-07 07:48:50.760</t>
         </is>
       </c>
     </row>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="I305" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:34.910</t>
+          <t>2026-08-07 07:48:50.930</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="I306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:35.080</t>
+          <t>2026-08-07 07:48:51.100</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="I307" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:35.250</t>
+          <t>2026-08-07 07:48:51.270</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="I308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:35.420</t>
+          <t>2026-08-07 07:48:51.440</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="I309" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:35.590</t>
+          <t>2026-08-07 07:48:51.610</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="I310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:35.760</t>
+          <t>2026-08-07 07:48:51.780</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="I311" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:35.930</t>
+          <t>2026-08-07 07:48:51.950</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="I312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:36.100</t>
+          <t>2026-08-07 07:48:52.120</t>
         </is>
       </c>
     </row>
@@ -13714,7 +13714,7 @@
       </c>
       <c r="I313" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:36.270</t>
+          <t>2026-08-07 07:48:52.290</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="I314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:36.440</t>
+          <t>2026-08-07 07:48:52.460</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="I315" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:36.610</t>
+          <t>2026-08-07 07:48:52.630</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="I316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:36.780</t>
+          <t>2026-08-07 07:48:52.800</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="I317" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:36.950</t>
+          <t>2026-08-07 07:48:52.970</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="I318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:37.120</t>
+          <t>2026-08-07 07:48:53.140</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="I319" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:37.290</t>
+          <t>2026-08-07 07:48:53.310</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:37.460</t>
+          <t>2026-08-07 07:48:53.480</t>
         </is>
       </c>
     </row>
@@ -14042,7 +14042,7 @@
       </c>
       <c r="I321" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:37.630</t>
+          <t>2026-08-07 07:48:53.650</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:37.800</t>
+          <t>2026-08-07 07:48:53.820</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14124,7 @@
       </c>
       <c r="I323" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:37.970</t>
+          <t>2026-08-07 07:48:53.990</t>
         </is>
       </c>
     </row>
@@ -14165,7 +14165,7 @@
       </c>
       <c r="I324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:38.140</t>
+          <t>2026-08-07 07:48:54.160</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="I325" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:38.310</t>
+          <t>2026-08-07 07:48:54.330</t>
         </is>
       </c>
     </row>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:38.480</t>
+          <t>2026-08-07 07:48:54.500</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="I327" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:38.650</t>
+          <t>2026-08-07 07:48:54.670</t>
         </is>
       </c>
     </row>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:38.820</t>
+          <t>2026-08-07 07:48:54.840</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="I329" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:38.990</t>
+          <t>2026-08-07 07:48:55.010</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:39.160</t>
+          <t>2026-08-07 07:48:55.180</t>
         </is>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="I331" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:39.330</t>
+          <t>2026-08-07 07:48:55.350</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:39.500</t>
+          <t>2026-08-07 07:48:55.520</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="I333" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:39.670</t>
+          <t>2026-08-07 07:48:55.690</t>
         </is>
       </c>
     </row>
@@ -14575,7 +14575,7 @@
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:39.840</t>
+          <t>2026-08-07 07:48:55.860</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="I335" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:40.010</t>
+          <t>2026-08-07 07:48:56.030</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:40.180</t>
+          <t>2026-08-07 07:48:56.200</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="I337" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:40.350</t>
+          <t>2026-08-07 07:48:56.370</t>
         </is>
       </c>
     </row>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:40.520</t>
+          <t>2026-08-07 07:48:56.540</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="I339" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:40.690</t>
+          <t>2026-08-07 07:48:56.710</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:40.860</t>
+          <t>2026-08-07 07:48:56.880</t>
         </is>
       </c>
     </row>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="I341" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:41.030</t>
+          <t>2026-08-07 07:48:57.050</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="I342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:41.200</t>
+          <t>2026-08-07 07:48:57.220</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="I343" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:41.370</t>
+          <t>2026-08-07 07:48:57.390</t>
         </is>
       </c>
     </row>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="I344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:41.540</t>
+          <t>2026-08-07 07:48:57.560</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="I345" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:41.710</t>
+          <t>2026-08-07 07:48:57.730</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:41.880</t>
+          <t>2026-08-07 07:48:57.900</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="I347" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:42.050</t>
+          <t>2026-08-07 07:48:58.070</t>
         </is>
       </c>
     </row>
@@ -15149,7 +15149,7 @@
       </c>
       <c r="I348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:42.220</t>
+          <t>2026-08-07 07:48:58.240</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="I349" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:42.390</t>
+          <t>2026-08-07 07:48:58.410</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="I350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:42.560</t>
+          <t>2026-08-07 07:48:58.580</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="I351" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27 03:38:42.730</t>
+          <t>2026-08-07 07:48:58.750</t>
         </is>
       </c>
     </row>
